--- a/APmap-tmpl-v20250804en.xlsx
+++ b/APmap-tmpl-v20250804en.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\git\apmapdb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC94FA2-329B-4D71-AECC-B59512090660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2D793B-4B39-4ABD-A844-800102825F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3672" yWindow="0" windowWidth="17844" windowHeight="12240" xr2:uid="{1C09F2BD-4AD8-448C-9B67-4E49C39AE540}"/>
+    <workbookView xWindow="2450" yWindow="5510" windowWidth="21070" windowHeight="15370" xr2:uid="{1C09F2BD-4AD8-448C-9B67-4E49C39AE540}"/>
   </bookViews>
   <sheets>
     <sheet name="APdata1" sheetId="2" r:id="rId1"/>
@@ -253,10 +253,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Do not modify the version.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>legend</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -400,6 +396,9 @@
   </si>
   <si>
     <t>production</t>
+  </si>
+  <si>
+    <t>&lt; Do not modify the template version.</t>
   </si>
 </sst>
 </file>
@@ -407,12 +406,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="177" formatCode="0_ "/>
-    <numFmt numFmtId="178" formatCode="0.0000000_ "/>
-    <numFmt numFmtId="179" formatCode="0.0000000"/>
+    <numFmt numFmtId="164" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="165" formatCode="0_ "/>
+    <numFmt numFmtId="166" formatCode="0.0000000_ "/>
+    <numFmt numFmtId="167" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="9"/>
       <color theme="1"/>
@@ -491,6 +490,13 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -556,7 +562,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -582,25 +588,25 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -612,7 +618,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -687,7 +693,7 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -704,6 +710,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -726,9 +735,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -766,7 +775,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -872,7 +881,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1014,7 +1023,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1022,44 +1031,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B35A389-7A8B-43CA-A10C-398A3B5E2FAA}">
-  <dimension ref="A1:Y19"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15"/>
+  <dimension ref="A1:Y18"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" style="8" customWidth="1"/>
-    <col min="5" max="5" width="20.88671875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.54296875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6328125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="19.90625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="20.90625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.08984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" style="13" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.33203125" style="14" customWidth="1"/>
-    <col min="13" max="13" width="11.33203125" style="23" customWidth="1"/>
-    <col min="14" max="14" width="14.6640625" style="23" customWidth="1"/>
-    <col min="15" max="15" width="13.109375" style="23" customWidth="1"/>
-    <col min="16" max="16" width="34.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.109375" style="23" customWidth="1"/>
-    <col min="18" max="18" width="23.88671875" style="23" customWidth="1"/>
+    <col min="11" max="12" width="13.36328125" style="14" customWidth="1"/>
+    <col min="13" max="13" width="11.36328125" style="23" customWidth="1"/>
+    <col min="14" max="14" width="14.6328125" style="23" customWidth="1"/>
+    <col min="15" max="15" width="13.08984375" style="23" customWidth="1"/>
+    <col min="16" max="16" width="34.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.08984375" style="23" customWidth="1"/>
+    <col min="18" max="18" width="23.90625" style="23" customWidth="1"/>
     <col min="19" max="19" width="15" style="23" customWidth="1"/>
-    <col min="20" max="20" width="58.33203125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="27.109375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="11.44140625" style="11" customWidth="1"/>
-    <col min="23" max="23" width="17.88671875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="25.33203125" style="35" customWidth="1"/>
-    <col min="25" max="25" width="11.6640625" style="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.109375" style="1"/>
+    <col min="20" max="20" width="58.36328125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="27.08984375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="11.453125" style="11" customWidth="1"/>
+    <col min="23" max="23" width="17.90625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="25.36328125" style="35" customWidth="1"/>
+    <col min="25" max="25" width="11.6328125" style="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="7"/>
+      <c r="C1" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="D1" s="2"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
@@ -1079,23 +1090,23 @@
       <c r="V1" s="12"/>
       <c r="W1" s="7"/>
     </row>
-    <row r="2" spans="1:25" ht="73.2" customHeight="1">
+    <row r="2" spans="1:25" ht="73.25" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>56</v>
       </c>
       <c r="C2" s="18"/>
       <c r="I2" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="L2" s="15" t="s">
         <v>58</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>59</v>
       </c>
       <c r="M2" s="20" t="s">
         <v>15</v>
@@ -1122,17 +1133,17 @@
         <v>18</v>
       </c>
       <c r="U2" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V2" s="2"/>
       <c r="W2" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="X2" s="36" t="s">
+      <c r="Y2" s="17" t="s">
         <v>62</v>
-      </c>
-      <c r="Y2" s="17" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:25" s="24" customFormat="1">
@@ -1314,72 +1325,72 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:25" s="3" customFormat="1" ht="57.6">
+    <row r="6" spans="1:25" s="3" customFormat="1" ht="54">
       <c r="A6" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="C6" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="D6" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="E6" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="47" t="s">
+      <c r="F6" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="47" t="s">
+      <c r="G6" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="46" t="s">
+      <c r="H6" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="J6" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="M6" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="N6" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="O6" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="P6" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q6" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="R6" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="S6" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="T6" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="U6" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="I6" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="J6" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="K6" s="47" t="s">
-        <v>83</v>
-      </c>
-      <c r="L6" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="M6" s="46" t="s">
-        <v>78</v>
-      </c>
-      <c r="N6" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="O6" s="46" t="s">
-        <v>80</v>
-      </c>
-      <c r="P6" s="46" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q6" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="R6" s="46" t="s">
-        <v>76</v>
-      </c>
-      <c r="S6" s="46" t="s">
-        <v>75</v>
-      </c>
-      <c r="T6" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="U6" s="46" t="s">
-        <v>73</v>
-      </c>
       <c r="V6" s="47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="W6" s="46" t="s">
         <v>14</v>
@@ -1388,15 +1399,15 @@
         <v>42</v>
       </c>
       <c r="Y6" s="42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:25" s="4" customFormat="1" ht="27.75" customHeight="1">
       <c r="A7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="C7" s="9">
         <v>45748</v>
@@ -1461,10 +1472,10 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="G8" s="2"/>
       <c r="I8" s="43"/>
@@ -1591,11 +1602,6 @@
     <row r="18" spans="1:2">
       <c r="B18" s="1" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="B19" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
